--- a/data/trans_bre/P1418-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1418-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>101,71%</t>
+          <t>109,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,12</t>
+          <t>0,51; 6,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,82</t>
+          <t>4,26; 9,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,72</t>
+          <t>1,71; 6,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,92</t>
+          <t>2,69; 6,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 142,66</t>
+          <t>6,03; 139,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>112,01; 475,29</t>
+          <t>100,05; 462,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,18; 275,95</t>
+          <t>38,35; 286,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,48; 189,67</t>
+          <t>44,86; 199,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>4,49</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>176,46%</t>
+          <t>114,09%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,43</t>
+          <t>1,68; 6,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,98</t>
+          <t>4,37; 8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,74</t>
+          <t>2,03; 5,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,73</t>
+          <t>2,84; 6,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,55; 138,01</t>
+          <t>24,19; 141,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,88; 315,54</t>
+          <t>93,19; 300,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,27; 324,11</t>
+          <t>61,09; 317,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,43; 438,93</t>
+          <t>57,72; 206,34</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 9,14</t>
+          <t>3,5; 9,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,94</t>
+          <t>2,11; 7,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,64</t>
+          <t>3,27; 7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,51</t>
+          <t>1,43; 5,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,37; 249,66</t>
+          <t>49,65; 240,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,49; 325,07</t>
+          <t>42,92; 349,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,01; 476,61</t>
+          <t>94,64; 514,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 112,87</t>
+          <t>26,3; 178,79</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>105,14%</t>
+          <t>120,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,87</t>
+          <t>2,92; 7,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,18</t>
+          <t>5,79; 10,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,63</t>
+          <t>3,65; 7,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,0</t>
+          <t>3,12; 6,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,41; 174,38</t>
+          <t>43,57; 164,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>150,93; 527,53</t>
+          <t>163,89; 571,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,04; 641,57</t>
+          <t>125,37; 608,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,38; 196,64</t>
+          <t>54,19; 201,56</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>106,08%</t>
+          <t>108,22%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,01</t>
+          <t>3,4; 5,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,86</t>
+          <t>5,41; 7,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,85</t>
+          <t>3,69; 5,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,57</t>
+          <t>3,57; 5,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,66; 125,54</t>
+          <t>56,74; 121,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>147,61; 293,13</t>
+          <t>150,65; 288,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>129,05; 276,79</t>
+          <t>131,9; 283,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,14; 160,16</t>
+          <t>75,24; 146,91</t>
         </is>
       </c>
     </row>
